--- a/test/contingent.xlsx
+++ b/test/contingent.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21F84B0-6AFF-4D71-9BF9-9C072E3B6BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Приклад" sheetId="3" r:id="rId1"/>
@@ -36,12 +37,25 @@
     <definedName name="Ф80" localSheetId="0">#REF!</definedName>
     <definedName name="Ф80">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="autoNoTable"/>
+  <calcPr calcId="191029" calcMode="autoNoTable"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="208">
   <si>
     <t>S</t>
   </si>
@@ -722,21 +736,6 @@
 «Гірництво та нафтогазові технології»</t>
   </si>
   <si>
-    <t xml:space="preserve">    Класний керівник Вєра МЄШКОВА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Класний керівник Оксана БОНДАРЕНКО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Класний керівник А... ТКАЧЕНКО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Класний керівник Олександра ВОЗІЯН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Класний керівник Дмитро ФЕДОРКАН</t>
-  </si>
-  <si>
     <t>Спеціальності E2, G1, G7</t>
   </si>
   <si>
@@ -763,12 +762,15 @@
     <t>«Харчові технології»,
 «Готельно-ресторанна справа та кейтеринг»,
 «Туризм та рекреація»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Класний керівник </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1091,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1148,14 +1150,11 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1196,50 +1195,47 @@
     <xf numFmtId="14" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 11 2" xfId="1"/>
+    <cellStyle name="Обычный 11 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1274,7 +1270,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1335,7 +1331,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1396,7 +1392,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1457,7 +1453,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1518,7 +1514,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1579,7 +1575,7 @@
         <xdr:cNvPr id="2" name="Прямая соединительная линия 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{37A70654-B778-46FC-BDF1-2E4EF96E21B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1621,9 +1617,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1661,9 +1657,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1698,7 +1694,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1733,7 +1729,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1906,7 +1902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1932,15 +1928,15 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -1957,71 +1953,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -2030,26 +2026,26 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
@@ -2059,7 +2055,7 @@
       <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="17" t="s">
@@ -2076,7 +2072,7 @@
       <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="17" t="s">
@@ -2093,7 +2089,7 @@
       <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -2110,7 +2106,7 @@
       <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="17" t="s">
@@ -2127,7 +2123,7 @@
       <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="17" t="s">
@@ -2144,7 +2140,7 @@
       <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="17" t="s">
@@ -2161,7 +2157,7 @@
       <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="17" t="s">
@@ -2178,7 +2174,7 @@
       <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="17" t="s">
@@ -2195,7 +2191,7 @@
       <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="17" t="s">
@@ -2212,7 +2208,7 @@
       <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="17" t="s">
@@ -2229,7 +2225,7 @@
       <c r="C20" s="17">
         <v>11</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>22</v>
       </c>
       <c r="E20" s="17" t="s">
@@ -2246,7 +2242,7 @@
       <c r="C21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="17" t="s">
@@ -2263,7 +2259,7 @@
       <c r="C22" s="17">
         <v>13</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -2280,7 +2276,7 @@
       <c r="C23" s="17">
         <v>14</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="17" t="s">
@@ -2297,7 +2293,7 @@
       <c r="C24" s="17">
         <v>15</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="17" t="s">
@@ -2314,7 +2310,7 @@
       <c r="C25" s="17">
         <v>16</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -2331,7 +2327,7 @@
       <c r="C26" s="17">
         <v>17</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="17" t="s">
@@ -2345,13 +2341,13 @@
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
@@ -2361,7 +2357,7 @@
       <c r="C28" s="17">
         <v>18</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -2378,7 +2374,7 @@
       <c r="C29" s="17">
         <v>19</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="17" t="s">
@@ -2395,7 +2391,7 @@
       <c r="C30" s="17">
         <v>20</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>32</v>
       </c>
       <c r="E30" s="17" t="s">
@@ -2412,7 +2408,7 @@
       <c r="C31" s="17">
         <v>21</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E31" s="17" t="s">
@@ -2429,7 +2425,7 @@
       <c r="C32" s="17">
         <v>22</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E32" s="17" t="s">
@@ -2446,7 +2442,7 @@
       <c r="C33" s="17">
         <v>23</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="17" t="s">
@@ -2463,7 +2459,7 @@
       <c r="C34" s="17">
         <v>24</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>36</v>
       </c>
       <c r="E34" s="17" t="s">
@@ -2480,7 +2476,7 @@
       <c r="C35" s="17">
         <v>25</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>37</v>
       </c>
       <c r="E35" s="17" t="s">
@@ -2497,7 +2493,7 @@
       <c r="C36" s="17">
         <v>26</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>38</v>
       </c>
       <c r="E36" s="17" t="s">
@@ -2514,7 +2510,7 @@
       <c r="C37" s="17">
         <v>27</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>39</v>
       </c>
       <c r="E37" s="17" t="s">
@@ -2531,7 +2527,7 @@
       <c r="C38" s="17">
         <v>28</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>40</v>
       </c>
       <c r="E38" s="17" t="s">
@@ -2545,105 +2541,105 @@
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="28">
+      <c r="C39" s="27">
         <v>29</v>
       </c>
-      <c r="D39" s="29" t="s">
+      <c r="D39" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="E39" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
+      <c r="E39" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="21"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="23"/>
+      <c r="C41" s="22"/>
       <c r="D41" s="16" t="s">
         <v>42</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
-      <c r="G41" s="24"/>
+      <c r="G41" s="23"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="23"/>
+      <c r="C42" s="22"/>
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
-      <c r="G42" s="24"/>
+      <c r="G42" s="23"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="32" t="e">
+      <c r="C43" s="22"/>
+      <c r="D43" s="39" t="e">
         <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C40,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C40,-1,0)) &amp; " студентів(а):")</f>
         <v>#REF!</v>
       </c>
-      <c r="E43" s="32"/>
+      <c r="E43" s="39"/>
       <c r="F43" s="16" t="e">
         <f ca="1">IF(D43="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=К"))</f>
         <v>#REF!</v>
       </c>
-      <c r="G43" s="24"/>
+      <c r="G43" s="23"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="23"/>
+      <c r="C44" s="22"/>
       <c r="D44" s="15"/>
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
-      <c r="G44" s="24"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="23"/>
+      <c r="C45" s="22"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="16" t="e">
         <f ca="1">IF(D43="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=Б"))</f>
         <v>#REF!</v>
       </c>
-      <c r="G45" s="24"/>
+      <c r="G45" s="23"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
@@ -2693,7 +2689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -2742,71 +2738,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -2815,216 +2811,216 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="30">
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29">
         <v>40245</v>
       </c>
-      <c r="G10" s="18"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="30">
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29">
         <v>39942</v>
       </c>
-      <c r="G11" s="18"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29">
         <v>40290</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="30">
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29">
         <v>40220</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="30">
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29">
         <v>40346</v>
       </c>
-      <c r="G14" s="18"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="30">
+      <c r="E15" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="29">
         <v>40068</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="30">
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29">
         <v>40418</v>
       </c>
-      <c r="G16" s="18"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="30">
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29">
         <v>40296</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="30">
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29">
         <v>40066</v>
       </c>
-      <c r="G18" s="18"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="30">
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29">
         <v>40165</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H19" s="10"/>
@@ -3033,76 +3029,76 @@
     <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="18">
-        <v>11</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="30">
+      <c r="E20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="29">
         <v>40086</v>
       </c>
-      <c r="G20" s="18"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="30">
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29">
         <v>40341</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="18">
-        <v>13</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="30">
+      <c r="E22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29">
         <v>40160</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <v>14</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="30">
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29">
         <v>40055</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H23" s="10"/>
@@ -3111,371 +3107,371 @@
     <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>15</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="30">
+      <c r="E24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="29">
         <v>39975</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <v>16</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="30">
+      <c r="E25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29">
         <v>40057</v>
       </c>
-      <c r="G25" s="18"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <v>17</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="30">
+      <c r="E26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29">
         <v>40059</v>
       </c>
-      <c r="G26" s="18"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <v>18</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="30">
+      <c r="E27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29">
         <v>39944</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>19</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="30">
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29">
         <v>40400</v>
       </c>
-      <c r="G28" s="18"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <v>20</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="30">
+      <c r="E29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="29">
         <v>40246</v>
       </c>
-      <c r="G29" s="18"/>
+      <c r="G29" s="17"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>21</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="30">
+      <c r="E31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29">
         <v>28964</v>
       </c>
-      <c r="G31" s="18"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>22</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="30">
+      <c r="E32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29">
         <v>37547</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="31">
+      <c r="C33" s="17">
         <v>23</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="30">
+      <c r="E33" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="29">
         <v>29882</v>
       </c>
-      <c r="G33" s="18"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="31">
+      <c r="C34" s="17">
         <v>24</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="30">
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29">
         <v>25471</v>
       </c>
-      <c r="G34" s="18"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="31">
+      <c r="C35" s="17">
         <v>25</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="30">
+      <c r="E35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29">
         <v>29416</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="31">
+      <c r="C36" s="17">
         <v>26</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="30">
+      <c r="E36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="29">
         <v>32150</v>
       </c>
-      <c r="G36" s="18"/>
+      <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="31">
+      <c r="C37" s="17">
         <v>27</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="30">
+      <c r="E37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="29">
         <v>32417</v>
       </c>
-      <c r="G37" s="18"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="31">
+      <c r="C38" s="17">
         <v>28</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="30">
+      <c r="E38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="29">
         <v>29045</v>
       </c>
-      <c r="G38" s="18"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="31">
+      <c r="C39" s="17">
         <v>29</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="30">
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29">
         <v>31743</v>
       </c>
-      <c r="G39" s="18"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="31">
+      <c r="C40" s="17">
         <v>30</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="30">
+      <c r="E40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="29">
         <v>28236</v>
       </c>
-      <c r="G40" s="18"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="31">
+      <c r="C41" s="17">
         <v>31</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="30">
+      <c r="E41" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="29">
         <v>27897</v>
       </c>
-      <c r="G41" s="18"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="31">
+      <c r="C42" s="17">
         <v>32</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="30">
+      <c r="E42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29">
         <v>36506</v>
       </c>
-      <c r="G42" s="18"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="31">
+      <c r="C43" s="17">
         <v>33</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="18" t="s">
         <v>82</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="29">
         <v>27714</v>
       </c>
       <c r="G43" s="17"/>
@@ -3485,13 +3481,13 @@
     <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
@@ -3501,13 +3497,13 @@
       <c r="C45" s="17">
         <v>34</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>66</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F45" s="30"/>
+      <c r="F45" s="29"/>
       <c r="G45" s="17"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
@@ -3515,13 +3511,13 @@
     <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
@@ -3531,13 +3527,13 @@
       <c r="C47" s="17">
         <v>35</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="18" t="s">
         <v>67</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="30">
+      <c r="F47" s="29">
         <v>39898</v>
       </c>
       <c r="G47" s="17"/>
@@ -3547,13 +3543,13 @@
     <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
       <c r="H48" s="10"/>
       <c r="I48" s="8"/>
     </row>
@@ -3563,13 +3559,13 @@
       <c r="C49" s="17">
         <v>36</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="18" t="s">
         <v>68</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="30">
+      <c r="F49" s="29">
         <v>26625</v>
       </c>
       <c r="G49" s="17"/>
@@ -3582,13 +3578,13 @@
       <c r="C50" s="17">
         <v>37</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="18" t="s">
         <v>69</v>
       </c>
       <c r="E50" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="30"/>
+      <c r="F50" s="29"/>
       <c r="G50" s="17"/>
       <c r="H50" s="10"/>
       <c r="I50" s="8"/>
@@ -3596,88 +3592,88 @@
     <row r="51" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="22"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="21"/>
       <c r="H51" s="10"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="9"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="24"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="23"/>
       <c r="H52" s="10"/>
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="9"/>
-      <c r="C53" s="23"/>
+      <c r="C53" s="22"/>
       <c r="D53" s="15"/>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
-      <c r="G53" s="24"/>
+      <c r="G53" s="23"/>
       <c r="H53" s="10"/>
       <c r="I53" s="8"/>
     </row>
     <row r="54" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="9"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="32" t="e">
-        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C51,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C51,-1,0)) &amp; " студентів(а):")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="16" t="e">
-        <f ca="1">IF(D54="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E51,-1,0),"=К"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G54" s="24"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C50)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C50) &amp; " студентів(а):")</f>
+        <v>Всього 37 студентів(а):</v>
+      </c>
+      <c r="E54" s="39"/>
+      <c r="F54" s="16" t="str">
+        <f>IF(D54="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E50,"=К"))</f>
+        <v>на контракті 21</v>
+      </c>
+      <c r="G54" s="23"/>
       <c r="H54" s="10"/>
       <c r="I54" s="8"/>
     </row>
     <row r="55" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="9"/>
-      <c r="C55" s="23"/>
+      <c r="C55" s="22"/>
       <c r="D55" s="15"/>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
-      <c r="G55" s="24"/>
+      <c r="G55" s="23"/>
       <c r="H55" s="10"/>
       <c r="I55" s="8"/>
     </row>
     <row r="56" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="9"/>
-      <c r="C56" s="23"/>
+      <c r="C56" s="22"/>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
-      <c r="F56" s="16" t="e">
-        <f ca="1">IF(D54="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E51,-1,0),"=Б"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G56" s="24"/>
+      <c r="F56" s="16" t="str">
+        <f>IF(D54="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E50,"=Б"))</f>
+        <v>на бюджеті 16</v>
+      </c>
+      <c r="G56" s="23"/>
       <c r="H56" s="10"/>
       <c r="I56" s="8"/>
     </row>
     <row r="57" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="9"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="27"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="26"/>
       <c r="H57" s="10"/>
       <c r="I57" s="8"/>
     </row>
@@ -3706,6 +3702,12 @@
   </sheetData>
   <sheetProtection insertRows="0" deleteRows="0"/>
   <mergeCells count="15">
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
@@ -3715,12 +3717,6 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="D52:F52"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
@@ -3730,7 +3726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3779,71 +3775,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -3852,745 +3848,745 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="18"/>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="18"/>
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="18"/>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="18"/>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="18"/>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="18"/>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="18"/>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="18"/>
+      <c r="E18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="18"/>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="18">
-        <v>11</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="18"/>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="18"/>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="18">
-        <v>13</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="18"/>
+      <c r="E22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <v>14</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="18"/>
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>15</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <v>16</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="18"/>
+      <c r="E26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <v>17</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="18"/>
+      <c r="E27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>18</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="18"/>
+      <c r="E28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <v>19</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="18"/>
+      <c r="E29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="17"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>20</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="30">
+      <c r="E31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29">
         <v>32690</v>
       </c>
-      <c r="G31" s="18"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>21</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="30">
+      <c r="E32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29">
         <v>29727</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="18">
+      <c r="C33" s="17">
         <v>22</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="18">
+      <c r="C34" s="17">
         <v>23</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="18"/>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="18">
+      <c r="C35" s="17">
         <v>24</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="30">
+      <c r="E35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29">
         <v>28919</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="18">
+      <c r="C36" s="17">
         <v>25</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="18"/>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="18">
+      <c r="C37" s="17">
         <v>26</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="30"/>
-      <c r="G37" s="18"/>
+      <c r="E37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="18">
+      <c r="C38" s="17">
         <v>27</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="18"/>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="18">
+      <c r="C39" s="17">
         <v>28</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="30">
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29">
         <v>28346</v>
       </c>
-      <c r="G39" s="18"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="18">
+      <c r="C40" s="17">
         <v>29</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E40" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="18"/>
+      <c r="E40" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="18">
+      <c r="C41" s="17">
         <v>30</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="18"/>
+      <c r="E41" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="18">
+      <c r="C42" s="17">
         <v>31</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="30"/>
-      <c r="G42" s="18"/>
+      <c r="E42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="18">
+      <c r="C43" s="17">
         <v>32</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E43" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="30">
+      <c r="E43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="29">
         <v>32461</v>
       </c>
-      <c r="G43" s="18"/>
+      <c r="G43" s="17"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="18">
+      <c r="C44" s="17">
         <v>33</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="30"/>
-      <c r="G44" s="18"/>
+      <c r="E44" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="17"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="18">
+      <c r="C45" s="17">
         <v>34</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E45" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="30"/>
-      <c r="G45" s="18"/>
+      <c r="E45" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="17"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>35</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="30"/>
-      <c r="G46" s="18"/>
+      <c r="E46" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="17"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="22"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
       <c r="H47" s="10"/>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="24"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="23"/>
       <c r="H48" s="10"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="23"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="24"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="10"/>
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="9"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="32" t="e">
-        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C47,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C47,-1,0)) &amp; " студентів(а):")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="16" t="e">
-        <f ca="1">IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E47,-1,0),"=К"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G50" s="24"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C46)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C46) &amp; " студентів(а):")</f>
+        <v>Всього 35 студентів(а):</v>
+      </c>
+      <c r="E50" s="39"/>
+      <c r="F50" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E46,"=К"))</f>
+        <v>на контракті 16</v>
+      </c>
+      <c r="G50" s="23"/>
       <c r="H50" s="10"/>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="23"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="24"/>
+      <c r="G51" s="23"/>
       <c r="H51" s="10"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="9"/>
-      <c r="C52" s="23"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
-      <c r="F52" s="16" t="e">
-        <f ca="1">IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E47,-1,0),"=Б"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G52" s="24"/>
+      <c r="F52" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E46,"=Б"))</f>
+        <v>на бюджеті 19</v>
+      </c>
+      <c r="G52" s="23"/>
       <c r="H52" s="10"/>
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="9"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="27"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
       <c r="H53" s="10"/>
       <c r="I53" s="8"/>
     </row>
@@ -4641,7 +4637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4690,71 +4686,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -4763,735 +4759,735 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="18"/>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="18"/>
+      <c r="E11" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="18"/>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="18"/>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="18"/>
+      <c r="E14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="18"/>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="18"/>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="18"/>
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="18"/>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="18">
-        <v>11</v>
-      </c>
-      <c r="D21" s="19" t="s">
+      <c r="C21" s="17">
+        <v>11</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="18"/>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="18">
+      <c r="C22" s="17">
         <v>12</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="18"/>
+      <c r="E22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="18">
-        <v>13</v>
-      </c>
-      <c r="D23" s="19" t="s">
+      <c r="C23" s="17">
+        <v>13</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="18"/>
+      <c r="E23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>14</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <v>15</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="18"/>
+      <c r="E25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <v>16</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="18"/>
+      <c r="E26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <v>17</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="18"/>
+      <c r="E27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>18</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="18"/>
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
+      <c r="C29" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <v>19</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="18"/>
+      <c r="E30" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>20</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="18"/>
+      <c r="E31" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>21</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="18"/>
+      <c r="E32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="18">
+      <c r="C33" s="17">
         <v>22</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="18">
+      <c r="C34" s="17">
         <v>23</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="18"/>
+      <c r="E34" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="18">
+      <c r="C35" s="17">
         <v>24</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="18"/>
+      <c r="E35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="18">
+      <c r="C36" s="17">
         <v>25</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="18"/>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="18">
+      <c r="C37" s="17">
         <v>26</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="30"/>
-      <c r="G37" s="18"/>
+      <c r="E37" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="18">
+      <c r="C38" s="17">
         <v>27</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="18"/>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="18">
+      <c r="C39" s="17">
         <v>28</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="30"/>
-      <c r="G39" s="18"/>
+      <c r="E39" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="18">
+      <c r="C40" s="17">
         <v>29</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E40" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="18"/>
+      <c r="E40" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="18">
+      <c r="C41" s="17">
         <v>30</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="18"/>
+      <c r="E41" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="18">
+      <c r="C42" s="17">
         <v>31</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="30"/>
-      <c r="G42" s="18"/>
+      <c r="E42" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="18">
+      <c r="C43" s="17">
         <v>32</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="E43" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="30"/>
-      <c r="G43" s="18"/>
+      <c r="E43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="17"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="18">
+      <c r="C44" s="17">
         <v>33</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="E44" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="30"/>
-      <c r="G44" s="18"/>
+      <c r="E44" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="17"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="18">
+      <c r="C45" s="17">
         <v>34</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E45" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="30"/>
-      <c r="G45" s="18"/>
+      <c r="E45" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="17"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="18">
+      <c r="C46" s="17">
         <v>35</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="E46" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="30"/>
-      <c r="G46" s="18"/>
+      <c r="E46" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="17"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="22"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
       <c r="H47" s="10"/>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="24"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="23"/>
       <c r="H48" s="10"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="23"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="24"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="10"/>
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="9"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="32" t="e">
-        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C47,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C47,-1,0)) &amp; " студентів(а):")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="16" t="e">
-        <f ca="1">IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E47,-1,0),"=К"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G50" s="24"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C46)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C46) &amp; " студентів(а):")</f>
+        <v>Всього 35 студентів(а):</v>
+      </c>
+      <c r="E50" s="39"/>
+      <c r="F50" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E46,"=К"))</f>
+        <v>на контракті 6</v>
+      </c>
+      <c r="G50" s="23"/>
       <c r="H50" s="10"/>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="23"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="24"/>
+      <c r="G51" s="23"/>
       <c r="H51" s="10"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="9"/>
-      <c r="C52" s="23"/>
+      <c r="C52" s="22"/>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
-      <c r="F52" s="16" t="e">
-        <f ca="1">IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E47,-1,0),"=Б"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G52" s="24"/>
+      <c r="F52" s="16" t="str">
+        <f>IF(D50="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E46,"=Б"))</f>
+        <v>на бюджеті 29</v>
+      </c>
+      <c r="G52" s="23"/>
       <c r="H52" s="10"/>
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="9"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="27"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
       <c r="H53" s="10"/>
       <c r="I53" s="8"/>
     </row>
@@ -5542,7 +5538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -5591,71 +5587,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -5664,620 +5660,620 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="C9" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="18"/>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="18"/>
+      <c r="E11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="18"/>
+      <c r="E12" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="18"/>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="18"/>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="18"/>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="18"/>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="18"/>
+      <c r="E18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="18"/>
+      <c r="E19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="18">
-        <v>11</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="18"/>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="18"/>
+      <c r="E21" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="18">
-        <v>13</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="18"/>
+      <c r="E22" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <v>14</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="18"/>
+      <c r="E23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="29"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>15</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <v>16</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="18"/>
+      <c r="E25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <v>17</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="18"/>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
+      <c r="C27" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>18</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="18"/>
+      <c r="E28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <v>19</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="18"/>
+      <c r="E29" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="17"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <v>20</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="18"/>
+      <c r="E30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>21</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="18"/>
+      <c r="E31" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>22</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="18"/>
+      <c r="E32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="18">
+      <c r="C33" s="17">
         <v>23</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="18">
+      <c r="C34" s="17">
         <v>24</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="18"/>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="18">
+      <c r="C35" s="17">
         <v>25</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="18"/>
+      <c r="E35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="18">
+      <c r="C36" s="17">
         <v>26</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="18"/>
+      <c r="E36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="18">
+      <c r="C37" s="17">
         <v>27</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="30"/>
-      <c r="G37" s="18"/>
+      <c r="E37" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="29"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="18">
+      <c r="C38" s="17">
         <v>28</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="18"/>
+      <c r="E38" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="18">
+      <c r="C39" s="17">
         <v>29</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="30"/>
-      <c r="G39" s="18"/>
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="21"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="24"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="23"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="23"/>
+      <c r="C42" s="22"/>
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
-      <c r="G42" s="24"/>
+      <c r="G42" s="23"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="32" t="e">
-        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C40,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C40,-1,0)) &amp; " студентів(а):")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="16" t="e">
-        <f ca="1">IF(D43="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=К"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G43" s="24"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C39)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C39) &amp; " студентів(а):")</f>
+        <v>Всього 29 студентів(а):</v>
+      </c>
+      <c r="E43" s="39"/>
+      <c r="F43" s="16" t="str">
+        <f>IF(D43="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E39,"=К"))</f>
+        <v>на контракті 8</v>
+      </c>
+      <c r="G43" s="23"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="23"/>
+      <c r="C44" s="22"/>
       <c r="D44" s="15"/>
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
-      <c r="G44" s="24"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="23"/>
+      <c r="C45" s="22"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
-      <c r="F45" s="16" t="e">
-        <f ca="1">IF(D43="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E40,-1,0),"=Б"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G45" s="24"/>
+      <c r="F45" s="16" t="str">
+        <f>IF(D43="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E39,"=Б"))</f>
+        <v>на бюджеті 21</v>
+      </c>
+      <c r="G45" s="23"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
@@ -6327,7 +6323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -6376,71 +6372,71 @@
     <row r="3" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="C3" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="10"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" s="11" customFormat="1" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="9"/>
-      <c r="C4" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="10"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="10"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="10"/>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9"/>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="40" t="s">
+      <c r="E7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="35" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10"/>
@@ -6449,667 +6445,667 @@
     <row r="8" spans="1:9" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="10"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="10"/>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9"/>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="18"/>
+      <c r="E10" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="29"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="10"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="9"/>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>2</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="18"/>
+      <c r="E11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="29"/>
+      <c r="G11" s="17"/>
       <c r="H11" s="10"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>3</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="18"/>
+      <c r="E12" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="10"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="9"/>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="18"/>
+      <c r="E13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="29"/>
+      <c r="G13" s="17"/>
       <c r="H13" s="10"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>5</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="18"/>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="29"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="10"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="9"/>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>6</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="18"/>
+      <c r="E15" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="29"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="10"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="9"/>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>7</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="29"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="10"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="18"/>
+      <c r="E17" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="29"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="10"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>9</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="18"/>
+      <c r="E18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="10"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>10</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="18"/>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="17"/>
       <c r="H19" s="10"/>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="18">
-        <v>11</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="C20" s="17">
+        <v>11</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="18"/>
+      <c r="E20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="29"/>
+      <c r="G20" s="17"/>
       <c r="H20" s="10"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="18"/>
+      <c r="E21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="10"/>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="18">
-        <v>13</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="17">
+        <v>13</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="18"/>
+      <c r="E22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="29"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="10"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
       <c r="H23" s="10"/>
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>14</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="18"/>
+      <c r="E24" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="10"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <v>15</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="18"/>
+      <c r="E25" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="10"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <v>16</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="18"/>
+      <c r="E26" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="10"/>
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <v>17</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="18"/>
+      <c r="E27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="10"/>
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <v>18</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="18"/>
+      <c r="E28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="10"/>
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <v>19</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="18"/>
+      <c r="E29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="17"/>
       <c r="H29" s="10"/>
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <v>20</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="18"/>
+      <c r="E30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="10"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="18">
+      <c r="C31" s="17">
         <v>21</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="18"/>
+      <c r="E31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="10"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>22</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="18"/>
+      <c r="E32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="10"/>
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="18">
+      <c r="C33" s="17">
         <v>23</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="18"/>
+      <c r="E33" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="10"/>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="18">
+      <c r="C34" s="17">
         <v>24</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="18"/>
+      <c r="E34" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="18">
+      <c r="C35" s="17">
         <v>25</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="18"/>
+      <c r="E35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="29"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="10"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="18">
+      <c r="C36" s="17">
         <v>26</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="18"/>
+      <c r="E36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="29"/>
+      <c r="G36" s="17"/>
       <c r="H36" s="10"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
       <c r="H37" s="10"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="18">
+      <c r="C38" s="17">
         <v>27</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="18"/>
+      <c r="E38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="10"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="18">
+      <c r="C39" s="17">
         <v>28</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="30"/>
-      <c r="G39" s="18"/>
+      <c r="E39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="10"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="18">
+      <c r="C40" s="17">
         <v>29</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="18"/>
+      <c r="E40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="10"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="18">
+      <c r="C41" s="17">
         <v>30</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="18"/>
+      <c r="E41" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="18">
+      <c r="C42" s="17">
         <v>31</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="30"/>
-      <c r="G42" s="18"/>
+      <c r="E42" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="10"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="22"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="21"/>
       <c r="H43" s="10"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="24"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="10"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="23"/>
+      <c r="C45" s="22"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
-      <c r="G45" s="24"/>
+      <c r="G45" s="23"/>
       <c r="H45" s="10"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="32" t="e">
-        <f ca="1">IF(COUNTBLANK(#REF!:OFFSET(C43,-1,0))&gt;0,"Очікую","Всього " &amp; COUNT(#REF!:OFFSET(C43,-1,0)) &amp; " студентів(а):")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="16" t="e">
-        <f ca="1">IF(D46="Очікую","Очікую","на контракті "&amp;COUNTIF(#REF!:OFFSET(E43,-1,0),"=К"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G46" s="24"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="39" t="str">
+        <f>IF(COUNTBLANK(C10:C42)&gt;0,"Очікую","Всього " &amp; COUNT(C10:C42) &amp; " студентів(а):")</f>
+        <v>Всього 31 студентів(а):</v>
+      </c>
+      <c r="E46" s="39"/>
+      <c r="F46" s="16" t="str">
+        <f>IF(D46="Очікую","Очікую","на контракті "&amp;COUNTIF(E10:E42,"=К"))</f>
+        <v>на контракті 18</v>
+      </c>
+      <c r="G46" s="23"/>
       <c r="H46" s="10"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="23"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="15"/>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="24"/>
+      <c r="G47" s="23"/>
       <c r="H47" s="10"/>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:9" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="23"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="15"/>
       <c r="E48" s="15"/>
-      <c r="F48" s="16" t="e">
-        <f ca="1">IF(D46="Очікую","Очікую","на бюджеті "&amp;COUNTIF(#REF!:OFFSET(E43,-1,0),"=Б"))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G48" s="24"/>
+      <c r="F48" s="16" t="str">
+        <f>IF(D46="Очікую","Очікую","на бюджеті "&amp;COUNTIF(E10:E42,"=Б"))</f>
+        <v>на бюджеті 13</v>
+      </c>
+      <c r="G48" s="23"/>
       <c r="H48" s="10"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" s="11" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="27"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="26"/>
       <c r="H49" s="10"/>
       <c r="I49" s="8"/>
     </row>
